--- a/data/xlsx/sbce_config_kvm_ems_sbce1_sbce2_sbce3_template.xlsx
+++ b/data/xlsx/sbce_config_kvm_ems_sbce1_sbce2_sbce3_template.xlsx
@@ -139,7 +139,7 @@
     <t xml:space="preserve">ip0</t>
   </si>
   <si>
-    <t xml:space="preserve">192.168.122.140</t>
+    <t xml:space="preserve">10.10.10.10</t>
   </si>
   <si>
     <t xml:space="preserve">Management IPv4 Address: (*) - The IPv4 address for the management interface.</t>
@@ -157,6 +157,9 @@
     <t xml:space="preserve">gateway</t>
   </si>
   <si>
+    <t xml:space="preserve">10.10.10.1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Default gateway: (*) - The IPv4 gateway for the management interface.</t>
   </si>
   <si>
@@ -307,9 +310,6 @@
     <t xml:space="preserve">M1</t>
   </si>
   <si>
-    <t xml:space="preserve">virbr0</t>
-  </si>
-  <si>
     <t xml:space="preserve">M1 NIC Port-group / Bridge name</t>
   </si>
   <si>
@@ -391,37 +391,37 @@
     <t xml:space="preserve">SBCE</t>
   </si>
   <si>
+    <t xml:space="preserve">sbceha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.10.10.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sbce2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.10.10.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1_sig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.10.11.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.10.11.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sbce3</t>
+  </si>
+  <si>
     <t xml:space="preserve">sbce</t>
   </si>
   <si>
-    <t xml:space="preserve">192.168.122.141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sbce2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.168.122.142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A1_sig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.168.122.151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sbce3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sbce-lab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.168.122.143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIP data interface (A1, A2, B1, B2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.168.122.152</t>
+    <t xml:space="preserve">10.10.10.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.10.11.11</t>
   </si>
 </sst>
 </file>
@@ -523,14 +523,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="21">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="20">
     <dxf>
       <fill>
         <patternFill>
@@ -912,7 +905,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C1048576"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.78"/>
@@ -1090,221 +1083,221 @@
         <v>43</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>64</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(B9, ".", B20)</f>
         <v>ems.lab.local</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>94</v>
@@ -1318,7 +1311,7 @@
         <v>96</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>97</v>
@@ -1414,109 +1407,105 @@
         <v>119</v>
       </c>
     </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <conditionalFormatting sqref="B13">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>B10&lt;&gt;"EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B50">
+  <conditionalFormatting sqref="B47">
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B47">
+  <conditionalFormatting sqref="B46">
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B46">
+  <conditionalFormatting sqref="B45">
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B45">
+  <conditionalFormatting sqref="B44">
     <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
-      <formula>B10="EMS"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B44">
+      <formula>B10&lt;&gt;"SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B43">
     <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>B10&lt;&gt;"SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B43">
+  <conditionalFormatting sqref="B42">
     <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
-      <formula>B10&lt;&gt;"SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B42">
+      <formula>B10="EMS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B41">
     <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B41">
+  <conditionalFormatting sqref="B40">
     <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B40">
+  <conditionalFormatting sqref="B39">
     <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B39">
+  <conditionalFormatting sqref="B32">
     <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
-      <formula>B10="EMS"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B32">
+      <formula>B10="EMS+SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31">
     <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>B10="EMS+SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B31">
+  <conditionalFormatting sqref="B26">
     <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
-      <formula>B10="EMS+SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
+      <formula>B10="SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25">
     <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B25">
+  <conditionalFormatting sqref="B24">
     <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B24">
+  <conditionalFormatting sqref="B23">
     <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B23">
+  <conditionalFormatting sqref="B22">
     <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
+  <conditionalFormatting sqref="B21">
     <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B21">
+  <conditionalFormatting sqref="B12">
     <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
-      <formula>B10="SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B12">
+      <formula>B10="EMS+SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5">
     <cfRule type="expression" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
-      <formula>B10="EMS+SBCE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5">
-    <cfRule type="expression" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
       <formula>B1="KVM"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1550,23 +1539,23 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
-      <formula1>$B$1="ESXI"</formula1>
+      <formula1>#ref!="ESXI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B31:B32" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula1>#ref!&lt;&gt;"EMS+SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
-      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B39:B42 B46:B47 B50" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS"</formula1>
+      <formula1>#ref!&lt;&gt;"SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B39:B42 B46:B47" type="custom">
+      <formula1>#ref!&lt;&gt;"EMS"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
-      <formula1>$B$10="SBCE"</formula1>
+      <formula1>#ref!="SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2 B14 B48:B49" type="none">
@@ -1775,224 +1764,224 @@
         <v>43</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>64</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(B9, ".", B20)</f>
         <v>sbce1.lab.local</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>94</v>
@@ -2006,7 +1995,7 @@
         <v>96</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>97</v>
@@ -2017,7 +2006,7 @@
         <v>98</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>99</v>
@@ -2028,7 +2017,7 @@
         <v>100</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>101</v>
@@ -2039,7 +2028,7 @@
         <v>102</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>103</v>
@@ -2050,7 +2039,7 @@
         <v>104</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>105</v>
@@ -2116,7 +2105,7 @@
         <v>116</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>4</v>
+        <v>127</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>117</v>
@@ -2127,7 +2116,7 @@
         <v>118</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>119</v>
@@ -2140,81 +2129,81 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>B10&lt;&gt;"SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>B10&lt;&gt;"SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>B10="EMS+SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>B10="EMS+SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24">
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>B10="EMS+SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>B1="KVM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="15">
+  <dataValidations count="17">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" promptTitle="Host IP or FQDN" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B3" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
@@ -2244,19 +2233,15 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
-      <formula1>$B$1="ESXI"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B31:B32" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula1>#ref!="ESXI"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B32" type="custom">
+      <formula1>#ref!&lt;&gt;"EMS+SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
-      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
-      <formula1>$B$10="SBCE"</formula1>
+      <formula1>#ref!&lt;&gt;"SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2 B14 B48:B49" type="none">
@@ -2272,7 +2257,19 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B46:B47" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS"</formula1>
+      <formula1>#ref!&lt;&gt;"EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B31" type="none">
+      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B44" type="none">
+      <formula1>$B$10="SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43" type="none">
+      <formula1>$B$10="SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -2469,224 +2466,224 @@
         <v>43</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>64</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(B9, ".", B20)</f>
         <v>sbce2.lab.local</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>94</v>
@@ -2700,7 +2697,7 @@
         <v>96</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>97</v>
@@ -2711,7 +2708,7 @@
         <v>98</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>99</v>
@@ -2722,7 +2719,7 @@
         <v>100</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>101</v>
@@ -2733,7 +2730,7 @@
         <v>102</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>103</v>
@@ -2744,7 +2741,7 @@
         <v>104</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>105</v>
@@ -2810,7 +2807,7 @@
         <v>116</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>4</v>
+        <v>127</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>117</v>
@@ -2821,7 +2818,7 @@
         <v>118</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>119</v>
@@ -2834,76 +2831,81 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B43:B44">
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+  <conditionalFormatting sqref="B44">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>B10&lt;&gt;"SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B43">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>B10&lt;&gt;"SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>B10="EMS+SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>B10="EMS+SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24">
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>B10="EMS+SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>B1="KVM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="15">
+  <dataValidations count="17">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" promptTitle="Host IP or FQDN" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B3" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
@@ -2933,19 +2935,15 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
-      <formula1>$B$1="ESXI"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B31:B32" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula1>#ref!="ESXI"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B32" type="custom">
+      <formula1>#ref!&lt;&gt;"EMS+SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
-      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
-      <formula1>$B$10="SBCE"</formula1>
+      <formula1>#ref!&lt;&gt;"SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2 B14 B48:B49" type="none">
@@ -2961,7 +2959,19 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B46:B47" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS"</formula1>
+      <formula1>#ref!&lt;&gt;"EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B31" type="none">
+      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B44" type="none">
+      <formula1>$B$10="SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43" type="none">
+      <formula1>$B$10="SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -3059,7 +3069,7 @@
         <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -3081,7 +3091,7 @@
         <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>25</v>
@@ -3103,7 +3113,7 @@
         <v>29</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>30</v>
@@ -3136,7 +3146,7 @@
         <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>39</v>
@@ -3158,224 +3168,224 @@
         <v>43</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>64</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(B9, ".", B20)</f>
         <v>sbce3.lab.local</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>94</v>
@@ -3389,7 +3399,7 @@
         <v>96</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>97</v>
@@ -3400,7 +3410,7 @@
         <v>98</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>99</v>
@@ -3411,7 +3421,7 @@
         <v>100</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>101</v>
@@ -3422,7 +3432,7 @@
         <v>102</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>103</v>
@@ -3433,7 +3443,7 @@
         <v>104</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>105</v>
@@ -3465,7 +3475,7 @@
         <v>98</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3495,7 +3505,7 @@
         <v>116</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>4</v>
+        <v>127</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>117</v>
@@ -3519,76 +3529,81 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B43:B44">
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+  <conditionalFormatting sqref="B44">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>B10&lt;&gt;"SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B43">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>B10&lt;&gt;"SBCE"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>B10="EMS+SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>B10="EMS+SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24">
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>B10="EMS+SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>B1="KVM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="15">
+  <dataValidations count="17">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" promptTitle="Host IP or FQDN" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B3" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
@@ -3618,19 +3633,15 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
-      <formula1>$B$1="ESXI"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B31:B32" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula1>#ref!="ESXI"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B32" type="custom">
+      <formula1>#ref!&lt;&gt;"EMS+SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
-      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
-      <formula1>$B$10="SBCE"</formula1>
+      <formula1>#ref!&lt;&gt;"SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2 B14 B48:B49" type="none">
@@ -3646,7 +3657,19 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B46:B47" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS"</formula1>
+      <formula1>#ref!&lt;&gt;"EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B31" type="none">
+      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B44" type="none">
+      <formula1>$B$10="SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43" type="none">
+      <formula1>$B$10="SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>

--- a/data/xlsx/sbce_config_kvm_ems_sbce1_sbce2_sbce3_template.xlsx
+++ b/data/xlsx/sbce_config_kvm_ems_sbce1_sbce2_sbce3_template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="EMS" sheetId="1" state="visible" r:id="rId3"/>
@@ -247,7 +247,7 @@
     <t xml:space="preserve">Time Zone - Time Zone in which device is located  (for example America/Edmonton)</t>
   </si>
   <si>
-    <t xml:space="preserve">ntpservers</t>
+    <t xml:space="preserve">ntpserver</t>
   </si>
   <si>
     <t xml:space="preserve">NTP Server Address: - The IPv4 address for NTP servers.</t>
